--- a/ter/dist/20261025_泰瑞達模型_v0.1.1.xlsx
+++ b/ter/dist/20261025_泰瑞達模型_v0.1.1.xlsx
@@ -4288,7 +4288,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4402,7 +4402,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4520,7 +4520,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4934,7 +4934,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5232,7 +5232,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5520,7 +5520,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5904,7 +5904,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6162,7 +6162,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6471,7 +6471,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7075,7 +7075,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7525,7 +7525,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7952,7 +7952,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8113,7 +8113,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8234,7 +8234,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8355,7 +8355,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8476,7 +8476,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8597,7 +8597,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -13319,7 +13319,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -13470,7 +13470,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/ter/dist/20261025_泰瑞達模型_v0.1.1.xlsx
+++ b/ter/dist/20261025_泰瑞達模型_v0.1.1.xlsx
@@ -7933,26 +7933,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8094,26 +8094,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8215,26 +8215,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8336,26 +8336,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8457,26 +8457,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8578,26 +8578,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
